--- a/results/ctim_vs_ctimg.xlsx
+++ b/results/ctim_vs_ctimg.xlsx
@@ -3,9 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="yelp_paper_h01" sheetId="1" r:id="rId1"/>
-    <sheet name="digg_items_K20" sheetId="2" r:id="rId2"/>
-    <sheet name="Complexity" sheetId="3" r:id="rId3"/>
-    <sheet name="Notes" sheetId="4" r:id="rId4"/>
+    <sheet name="digg_paper_h01" sheetId="2" r:id="rId2"/>
+    <sheet name="epinions_paper_h01" sheetId="3" r:id="rId3"/>
+    <sheet name="ciao_paper_h01" sheetId="4" r:id="rId4"/>
+    <sheet name="lastfm_paper_h01" sheetId="5" r:id="rId5"/>
+    <sheet name="delicious_paper_h01" sheetId="6" r:id="rId6"/>
+    <sheet name="Complexity" sheetId="7" r:id="rId7"/>
+    <sheet name="Notes" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -696,7 +700,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">digg_items_K20.log -- K=20, h_sel=0.1, h_eval=0.05, seed=42</t>
+          <t xml:space="preserve">digg_paper_h01.log -- K=20, h_sel=0.1, h_eval=0.1, seed=42</t>
         </is>
       </c>
     </row>
@@ -709,152 +713,86 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CIRCULAR: graded at the same threshold used to select (the paper's protocol). CTIM-G maximises this objective directly, so its gap is an upper bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">#</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">item</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">method</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">I @ h_eval</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">gap</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">I @ h_sel</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">select</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Eq (12)</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">scoring</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">item total</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">|S|</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">MC-IC</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">SE</t>
         </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2369</v>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CTIM</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>778.6047</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>761.404</v>
-      </c>
-      <c r="G5" s="3">
-        <v>3.73</v>
-      </c>
-      <c r="H5" s="3">
-        <v>32.11</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1.78</v>
-      </c>
-      <c r="J5" s="3">
-        <v>108.27</v>
-      </c>
-      <c r="K5" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>2369</v>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CTIM-G</t>
-        </is>
-      </c>
-      <c r="D6" s="2">
-        <v>770.8483</v>
-      </c>
-      <c r="E6" s="4">
-        <v>-0.9961922911587817</v>
-      </c>
-      <c r="F6" s="2">
-        <v>763.8906</v>
-      </c>
-      <c r="G6" s="3">
-        <v>10.25</v>
-      </c>
-      <c r="H6" s="3">
-        <v>32.11</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1.78</v>
-      </c>
-      <c r="J6" s="3">
-        <v>108.27</v>
-      </c>
-      <c r="K6" s="7">
-        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="7">
-        <v>1113</v>
+        <v>2369</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -862,25 +800,25 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <v>778.6277</v>
+        <v>761.404</v>
       </c>
       <c r="E7" s="4">
         <v>0.0</v>
       </c>
       <c r="F7" s="2">
-        <v>761.5153</v>
+        <v>761.404</v>
       </c>
       <c r="G7" s="3">
-        <v>3.58</v>
+        <v>2.42</v>
       </c>
       <c r="H7" s="3">
-        <v>1.56</v>
+        <v>33.5</v>
       </c>
       <c r="I7" s="3">
-        <v>1.91</v>
+        <v>1.0</v>
       </c>
       <c r="J7" s="3">
-        <v>73.32</v>
+        <v>50.24</v>
       </c>
       <c r="K7" s="7">
         <v>20</v>
@@ -888,10 +826,10 @@
     </row>
     <row r="8">
       <c r="A8" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="7">
-        <v>1113</v>
+        <v>2369</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -899,25 +837,25 @@
         </is>
       </c>
       <c r="D8" s="2">
-        <v>770.8711</v>
+        <v>763.8906</v>
       </c>
       <c r="E8" s="4">
-        <v>-0.9961885507027368</v>
+        <v>0.3265808952934268</v>
       </c>
       <c r="F8" s="2">
-        <v>764.0019</v>
+        <v>763.8906</v>
       </c>
       <c r="G8" s="3">
-        <v>9.29</v>
+        <v>10.41</v>
       </c>
       <c r="H8" s="3">
-        <v>1.56</v>
+        <v>33.5</v>
       </c>
       <c r="I8" s="3">
-        <v>1.91</v>
+        <v>1.0</v>
       </c>
       <c r="J8" s="3">
-        <v>73.32</v>
+        <v>50.24</v>
       </c>
       <c r="K8" s="7">
         <v>20</v>
@@ -925,10 +863,10 @@
     </row>
     <row r="9">
       <c r="A9" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="7">
-        <v>535</v>
+        <v>1113</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -936,25 +874,25 @@
         </is>
       </c>
       <c r="D9" s="2">
-        <v>778.6842</v>
+        <v>761.5153</v>
       </c>
       <c r="E9" s="4">
         <v>0.0</v>
       </c>
       <c r="F9" s="2">
-        <v>761.6496</v>
+        <v>761.5153</v>
       </c>
       <c r="G9" s="3">
-        <v>3.71</v>
+        <v>2.36</v>
       </c>
       <c r="H9" s="3">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="I9" s="3">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="J9" s="3">
-        <v>80.73</v>
+        <v>18.37</v>
       </c>
       <c r="K9" s="7">
         <v>20</v>
@@ -962,252 +900,246 @@
     </row>
     <row r="10">
       <c r="A10" s="7">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7">
+        <v>1113</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>764.0019</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.3265331635490476</v>
+      </c>
+      <c r="F10" s="2">
+        <v>764.0019</v>
+      </c>
+      <c r="G10" s="3">
+        <v>11.02</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1.67</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="J10" s="3">
+        <v>18.37</v>
+      </c>
+      <c r="K10" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7">
         <v>3</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B11" s="7">
         <v>535</v>
       </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CTIM-G</t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>770.9269</v>
-      </c>
-      <c r="E10" s="4">
-        <v>-0.9962061641933917</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>761.6496</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>761.6496</v>
+      </c>
+      <c r="G11" s="3">
+        <v>2.42</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1.03</v>
+      </c>
+      <c r="J11" s="3">
+        <v>18.34</v>
+      </c>
+      <c r="K11" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7">
+        <v>535</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
         <v>764.1362</v>
       </c>
-      <c r="G10" s="3">
-        <v>11.12</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1.62</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1.91</v>
-      </c>
-      <c r="J10" s="3">
-        <v>80.73</v>
-      </c>
-      <c r="K10" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="E12" s="4">
+        <v>0.3264755866739799</v>
+      </c>
+      <c r="F12" s="2">
+        <v>764.1362</v>
+      </c>
+      <c r="G12" s="3">
+        <v>11.39</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1.03</v>
+      </c>
+      <c r="J12" s="3">
+        <v>18.34</v>
+      </c>
+      <c r="K12" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">mean</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CTIM</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>778.6388666666667</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="3">
-        <v>3.6733333333333333</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CTIM-G</t>
-        </is>
-      </c>
-      <c r="D14" s="2">
-        <v>770.8820999999999</v>
-      </c>
-      <c r="E14" s="4">
-        <v>-0.9961956686849701</v>
-      </c>
-      <c r="G14" s="3">
-        <v>10.219999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
+        <v>761.5229666666668</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D16" s="2">
+        <v>764.0095666666666</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.3265298818388181</v>
+      </c>
+      <c r="G16" s="3">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">CTIM-G / CTIM wall clock</t>
         </is>
       </c>
-      <c r="D15" s="6">
-        <v>2.7822141560798546</v>
-      </c>
-      <c r="E15" s="0" t="inlineStr">
+      <c r="D17" s="6">
+        <v>4.558333333333334</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">x</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Phase breakdown (seconds, and % of that method's select time)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">#</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">item</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">method</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">mia</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">solo</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">curves</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">dp</t>
         </is>
       </c>
-      <c r="H18" s="1" t="inlineStr">
+      <c r="H20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">realise</t>
         </is>
       </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="I20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">repair</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr">
+      <c r="J20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">select</t>
         </is>
       </c>
-      <c r="K18" s="1" t="inlineStr">
+      <c r="K20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">unattributed</t>
         </is>
       </c>
-      <c r="L18" s="1" t="inlineStr">
+      <c r="L20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">curves %</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7">
-        <v>1</v>
-      </c>
-      <c r="B19" s="7">
-        <v>2369</v>
-      </c>
-      <c r="C19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CTIM-G</t>
-        </is>
-      </c>
-      <c r="D19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1.05</v>
-      </c>
-      <c r="F19" s="3">
-        <v>7.16</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="H19" s="3">
-        <v>1.43</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="3">
-        <v>10.25</v>
-      </c>
-      <c r="K19" s="3">
-        <v>0.5999999999999996</v>
-      </c>
-      <c r="L19" s="6">
-        <v>69.85365853658537</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7">
-        <v>2</v>
-      </c>
-      <c r="B20" s="7">
-        <v>1113</v>
-      </c>
-      <c r="C20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CTIM-G</t>
-        </is>
-      </c>
-      <c r="D20" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1.03</v>
-      </c>
-      <c r="F20" s="3">
-        <v>6.42</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1.25</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>9.29</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0.5899999999999999</v>
-      </c>
-      <c r="L20" s="6">
-        <v>69.1065662002153</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B21" s="7">
-        <v>535</v>
+        <v>2369</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -1218,39 +1150,119 @@
         <v>0.0</v>
       </c>
       <c r="E21" s="3">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="F21" s="3">
-        <v>7.68</v>
+        <v>7.39</v>
       </c>
       <c r="G21" s="3">
         <v>0.01</v>
       </c>
       <c r="H21" s="3">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="I21" s="3">
         <v>0.0</v>
       </c>
       <c r="J21" s="3">
-        <v>11.12</v>
+        <v>10.41</v>
       </c>
       <c r="K21" s="3">
-        <v>0.629999999999999</v>
+        <v>0.45000000000000107</v>
       </c>
       <c r="L21" s="6">
-        <v>69.06474820143886</v>
-      </c>
-    </row>
-    <row r="22"/>
+        <v>70.98943323727185</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7">
+        <v>1113</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1.12</v>
+      </c>
+      <c r="F22" s="3">
+        <v>7.71</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1.54</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>11.02</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0.6399999999999988</v>
+      </c>
+      <c r="L22" s="6">
+        <v>69.96370235934664</v>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="0" t="inlineStr">
+      <c r="A23" s="7">
+        <v>3</v>
+      </c>
+      <c r="B23" s="7">
+        <v>535</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="F23" s="3">
+        <v>8.18</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1.62</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>11.39</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0.6400000000000006</v>
+      </c>
+      <c r="L23" s="6">
+        <v>71.81738366988586</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">TOTAL for the whole log</t>
         </is>
       </c>
-      <c r="B23" s="3">
-        <v>267.09</v>
+      <c r="B25" s="3">
+        <v>91.65</v>
       </c>
     </row>
   </sheetData>
@@ -1258,6 +1270,2366 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epinions_paper_h01.log -- K=20, h_sel=0.1, h_eval=0.1, seed=42</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U=18059  E=354897  C=100   test_items=[385, 4024, 665]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CIRCULAR: graded at the same threshold used to select (the paper's protocol). CTIM-G maximises this objective directly, so its gap is an upper bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">method</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I @ h_eval</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I @ h_sel</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">select</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eq (12)</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scoring</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item total</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|S|</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MC-IC</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7">
+        <v>385</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>1442.5593</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1442.5593</v>
+      </c>
+      <c r="G7" s="3">
+        <v>18.4</v>
+      </c>
+      <c r="H7" s="3">
+        <v>23.66</v>
+      </c>
+      <c r="I7" s="3">
+        <v>9.27</v>
+      </c>
+      <c r="J7" s="3">
+        <v>119.15</v>
+      </c>
+      <c r="K7" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7">
+        <v>385</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>1540.4405</v>
+      </c>
+      <c r="E8" s="4">
+        <v>6.785246194038619</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1540.4405</v>
+      </c>
+      <c r="G8" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="H8" s="3">
+        <v>23.66</v>
+      </c>
+      <c r="I8" s="3">
+        <v>9.27</v>
+      </c>
+      <c r="J8" s="3">
+        <v>119.15</v>
+      </c>
+      <c r="K8" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4024</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>1442.4877</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1442.4877</v>
+      </c>
+      <c r="G9" s="3">
+        <v>18.01</v>
+      </c>
+      <c r="H9" s="3">
+        <v>5.77</v>
+      </c>
+      <c r="I9" s="3">
+        <v>9.33</v>
+      </c>
+      <c r="J9" s="3">
+        <v>100.2</v>
+      </c>
+      <c r="K9" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7">
+        <v>4024</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>1540.2607</v>
+      </c>
+      <c r="E10" s="4">
+        <v>6.778082059209245</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1540.2607</v>
+      </c>
+      <c r="G10" s="3">
+        <v>60.66</v>
+      </c>
+      <c r="H10" s="3">
+        <v>5.77</v>
+      </c>
+      <c r="I10" s="3">
+        <v>9.33</v>
+      </c>
+      <c r="J10" s="3">
+        <v>100.2</v>
+      </c>
+      <c r="K10" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7">
+        <v>3</v>
+      </c>
+      <c r="B11" s="7">
+        <v>665</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>1442.5238</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1442.5238</v>
+      </c>
+      <c r="G11" s="3">
+        <v>18.19</v>
+      </c>
+      <c r="H11" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="I11" s="3">
+        <v>9.76</v>
+      </c>
+      <c r="J11" s="3">
+        <v>101.22</v>
+      </c>
+      <c r="K11" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7">
+        <v>665</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <v>1540.401</v>
+      </c>
+      <c r="E12" s="4">
+        <v>6.785135884759752</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1540.401</v>
+      </c>
+      <c r="G12" s="3">
+        <v>61.17</v>
+      </c>
+      <c r="H12" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="I12" s="3">
+        <v>9.76</v>
+      </c>
+      <c r="J12" s="3">
+        <v>101.22</v>
+      </c>
+      <c r="K12" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
+        <v>1442.5235999999998</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D16" s="2">
+        <v>1540.3674</v>
+      </c>
+      <c r="E16" s="4">
+        <v>6.782821379335871</v>
+      </c>
+      <c r="G16" s="3">
+        <v>60.71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G / CTIM wall clock</t>
+        </is>
+      </c>
+      <c r="D17" s="6">
+        <v>3.335714285714286</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phase breakdown (seconds, and % of that method's select time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">method</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mia</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solo</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curves</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dp</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">realise</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">select</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unattributed</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curves %</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7">
+        <v>385</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6.82</v>
+      </c>
+      <c r="F21" s="3">
+        <v>44.93</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H21" s="3">
+        <v>7.65</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0.8899999999999935</v>
+      </c>
+      <c r="L21" s="6">
+        <v>74.51077943615257</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7">
+        <v>4024</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>7.42</v>
+      </c>
+      <c r="F22" s="3">
+        <v>44.33</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H22" s="3">
+        <v>7.63</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>60.66</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1.269999999999996</v>
+      </c>
+      <c r="L22" s="6">
+        <v>73.0794592812397</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7">
+        <v>3</v>
+      </c>
+      <c r="B23" s="7">
+        <v>665</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>6.85</v>
+      </c>
+      <c r="F23" s="3">
+        <v>45.43</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H23" s="3">
+        <v>7.68</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>61.17</v>
+      </c>
+      <c r="K23" s="3">
+        <v>1.2000000000000028</v>
+      </c>
+      <c r="L23" s="6">
+        <v>74.26843223802517</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL for the whole log</t>
+        </is>
+      </c>
+      <c r="B25" s="3">
+        <v>325.55</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ciao_paper_h01.log -- K=20, h_sel=0.1, h_eval=0.1, seed=42</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U=2215  E=52721  C=100   test_items=[415, 4387, 4571]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CIRCULAR: graded at the same threshold used to select (the paper's protocol). CTIM-G maximises this objective directly, so its gap is an upper bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">method</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I @ h_eval</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I @ h_sel</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">select</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eq (12)</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scoring</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item total</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|S|</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MC-IC</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7">
+        <v>415</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>120.5889</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>120.5889</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="H7" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="J7" s="3">
+        <v>8.64</v>
+      </c>
+      <c r="K7" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7">
+        <v>415</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>118.193</v>
+      </c>
+      <c r="E8" s="4">
+        <v>-1.9868329506281257</v>
+      </c>
+      <c r="F8" s="2">
+        <v>118.193</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="J8" s="3">
+        <v>8.64</v>
+      </c>
+      <c r="K8" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4387</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>120.6815</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>120.6815</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.17</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="J9" s="3">
+        <v>6.12</v>
+      </c>
+      <c r="K9" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7">
+        <v>4387</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>118.1959</v>
+      </c>
+      <c r="E10" s="4">
+        <v>-2.059636315425317</v>
+      </c>
+      <c r="F10" s="2">
+        <v>118.1959</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="J10" s="3">
+        <v>6.12</v>
+      </c>
+      <c r="K10" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7">
+        <v>3</v>
+      </c>
+      <c r="B11" s="7">
+        <v>4571</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>119.9672</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>119.9672</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1.12</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="J11" s="3">
+        <v>6.28</v>
+      </c>
+      <c r="K11" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7">
+        <v>4571</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <v>118.2075</v>
+      </c>
+      <c r="E12" s="4">
+        <v>-1.4668175968097996</v>
+      </c>
+      <c r="F12" s="2">
+        <v>118.2075</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2.82</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="J12" s="3">
+        <v>6.28</v>
+      </c>
+      <c r="K12" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
+        <v>120.41253333333333</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1.1766666666666667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D16" s="2">
+        <v>118.1988</v>
+      </c>
+      <c r="E16" s="4">
+        <v>-1.837762287621081</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2.813333333333333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G / CTIM wall clock</t>
+        </is>
+      </c>
+      <c r="D17" s="6">
+        <v>2.390934844192634</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phase breakdown (seconds, and % of that method's select time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">method</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mia</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solo</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curves</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dp</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">realise</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">select</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unattributed</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curves %</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7">
+        <v>415</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1.74</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L21" s="6">
+        <v>63.970588235294116</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7">
+        <v>4387</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1.83</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="L22" s="6">
+        <v>63.10344827586207</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7">
+        <v>3</v>
+      </c>
+      <c r="B23" s="7">
+        <v>4571</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1.76</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.71</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>2.82</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0.11999999999999966</v>
+      </c>
+      <c r="L23" s="6">
+        <v>62.4113475177305</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL for the whole log</t>
+        </is>
+      </c>
+      <c r="B25" s="3">
+        <v>21.38</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lastfm_paper_h01.log -- K=20, h_sel=0.1, h_eval=0.1, seed=42</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U=1892  E=25434  C=100   test_items=[86, 251, 69]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CIRCULAR: graded at the same threshold used to select (the paper's protocol). CTIM-G maximises this objective directly, so its gap is an upper bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">method</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I @ h_eval</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I @ h_sel</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">select</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eq (12)</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scoring</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item total</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|S|</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MC-IC</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7">
+        <v>86</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>83.4763</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>83.4763</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.07</v>
+      </c>
+      <c r="J7" s="3">
+        <v>4.02</v>
+      </c>
+      <c r="K7" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7">
+        <v>86</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>81.7176</v>
+      </c>
+      <c r="E8" s="4">
+        <v>-2.106825530120515</v>
+      </c>
+      <c r="F8" s="2">
+        <v>81.7176</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.07</v>
+      </c>
+      <c r="J8" s="3">
+        <v>4.02</v>
+      </c>
+      <c r="K8" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>251</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>85.6152</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>85.6152</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1.93</v>
+      </c>
+      <c r="K9" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7">
+        <v>251</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>83.7831</v>
+      </c>
+      <c r="E10" s="4">
+        <v>-2.1399237518571423</v>
+      </c>
+      <c r="F10" s="2">
+        <v>83.7831</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1.93</v>
+      </c>
+      <c r="K10" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7">
+        <v>3</v>
+      </c>
+      <c r="B11" s="7">
+        <v>69</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>65.6504</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>65.6504</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1.47</v>
+      </c>
+      <c r="K11" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7">
+        <v>69</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <v>64.173</v>
+      </c>
+      <c r="E12" s="4">
+        <v>-2.250405176510739</v>
+      </c>
+      <c r="F12" s="2">
+        <v>64.173</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1.47</v>
+      </c>
+      <c r="K12" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
+        <v>78.2473</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.4266666666666667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D16" s="2">
+        <v>76.5579</v>
+      </c>
+      <c r="E16" s="4">
+        <v>-2.1657181528294656</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.3933333333333333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G / CTIM wall clock</t>
+        </is>
+      </c>
+      <c r="D17" s="6">
+        <v>0.9218749999999999</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phase breakdown (seconds, and % of that method's select time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">method</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mia</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solo</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curves</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dp</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">realise</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">select</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unattributed</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curves %</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7">
+        <v>86</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0.04999999999999999</v>
+      </c>
+      <c r="L21" s="6">
+        <v>48.78048780487805</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7">
+        <v>251</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0.04999999999999999</v>
+      </c>
+      <c r="L22" s="6">
+        <v>47.826086956521735</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7">
+        <v>3</v>
+      </c>
+      <c r="B23" s="7">
+        <v>69</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0.04999999999999999</v>
+      </c>
+      <c r="L23" s="6">
+        <v>48.38709677419355</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL for the whole log</t>
+        </is>
+      </c>
+      <c r="B25" s="3">
+        <v>7.81</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delicious_paper_h01.log -- K=20, h_sel=0.1, h_eval=0.1, seed=42</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U=1861  E=15328  C=100   test_items=[3170, 23, 33859]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CIRCULAR: graded at the same threshold used to select (the paper's protocol). CTIM-G maximises this objective directly, so its gap is an upper bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">method</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I @ h_eval</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I @ h_sel</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">select</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eq (12)</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scoring</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item total</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|S|</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MC-IC</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7">
+        <v>3170</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>23.0305</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>23.0305</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2.29</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>2.75</v>
+      </c>
+      <c r="K7" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7">
+        <v>3170</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>23.0305</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>23.0305</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.07</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2.29</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2.75</v>
+      </c>
+      <c r="K8" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>23</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>23.0308</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>23.0308</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="K9" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7">
+        <v>23</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>23.0308</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>23.0308</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="K10" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7">
+        <v>3</v>
+      </c>
+      <c r="B11" s="7">
+        <v>33859</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>23.0327</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>23.0327</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.69</v>
+      </c>
+      <c r="K11" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7">
+        <v>33859</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <v>23.0327</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>23.0327</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.69</v>
+      </c>
+      <c r="K12" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
+        <v>23.031333333333333</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.05333333333333334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D16" s="2">
+        <v>23.031333333333333</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G / CTIM wall clock</t>
+        </is>
+      </c>
+      <c r="D17" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phase breakdown (seconds, and % of that method's select time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">method</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mia</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solo</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curves</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dp</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">realise</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">select</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unattributed</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curves %</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7">
+        <v>3170</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.07</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0.04000000000000001</v>
+      </c>
+      <c r="L21" s="6">
+        <v>14.285714285714285</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7">
+        <v>23</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="L22" s="6">
+        <v>16.666666666666668</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7">
+        <v>3</v>
+      </c>
+      <c r="B23" s="7">
+        <v>33859</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="D23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="L23" s="6">
+        <v>9.090909090909092</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL for the whole log</t>
+        </is>
+      </c>
+      <c r="B25" s="3">
+        <v>5.12</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1432,7 +3804,7 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">digg_items_K20</t>
+          <t xml:space="preserve">digg_paper_h01</t>
         </is>
       </c>
       <c r="B6" s="7">
@@ -1458,13 +3830,13 @@
         </is>
       </c>
       <c r="L6" s="3">
-        <v>3.6733333333333333</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">digg_items_K20</t>
+          <t xml:space="preserve">digg_paper_h01</t>
         </is>
       </c>
       <c r="B7" s="7">
@@ -1502,22 +3874,338 @@
         <v>127.66666666666667</v>
       </c>
       <c r="L7" s="3">
-        <v>10.219999999999999</v>
+        <v>10.94</v>
       </c>
       <c r="M7" s="2">
-        <v>0.2866679756528568</v>
-      </c>
-    </row>
-    <row r="8"/>
+        <v>0.3068637625873047</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epinions_paper_h01</t>
+        </is>
+      </c>
+      <c r="B8" s="7">
+        <v>18059</v>
+      </c>
+      <c r="C8" s="7">
+        <v>354897</v>
+      </c>
+      <c r="D8" s="7">
+        <v>100</v>
+      </c>
+      <c r="E8" s="7">
+        <v>20</v>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O(nC)  Eq (19)  +  sum_c O(n_c * t_c log t_c)  init  +  O(CK) DP cells</t>
+        </is>
+      </c>
+      <c r="L8" s="3">
+        <v>18.2</v>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epinions_paper_h01</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <v>18059</v>
+      </c>
+      <c r="C9" s="7">
+        <v>354897</v>
+      </c>
+      <c r="D9" s="7">
+        <v>100</v>
+      </c>
+      <c r="E9" s="7">
+        <v>20</v>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O(n * t log t)  global init  +  sum_c O(n_c * t log t)  curves  +  O(C K^2) DP  +  O(K * t^2) realisation</t>
+        </is>
+      </c>
+      <c r="H9" s="7">
+        <v>27215.666666666668</v>
+      </c>
+      <c r="I9" s="6">
+        <v>9.3</v>
+      </c>
+      <c r="J9" s="7">
+        <v>4314.666666666667</v>
+      </c>
+      <c r="K9" s="7">
+        <v>108.0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>60.71</v>
+      </c>
+      <c r="M9" s="2">
+        <v>2.23070045439514</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ciao_paper_h01</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <v>2215</v>
+      </c>
+      <c r="C10" s="7">
+        <v>52721</v>
+      </c>
+      <c r="D10" s="7">
+        <v>100</v>
+      </c>
+      <c r="E10" s="7">
+        <v>20</v>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O(nC)  Eq (19)  +  sum_c O(n_c * t_c log t_c)  init  +  O(CK) DP cells</t>
+        </is>
+      </c>
+      <c r="L10" s="3">
+        <v>1.1766666666666667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ciao_paper_h01</t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <v>2215</v>
+      </c>
+      <c r="C11" s="7">
+        <v>52721</v>
+      </c>
+      <c r="D11" s="7">
+        <v>100</v>
+      </c>
+      <c r="E11" s="7">
+        <v>20</v>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O(n * t log t)  global init  +  sum_c O(n_c * t log t)  curves  +  O(C K^2) DP  +  O(K * t^2) realisation</t>
+        </is>
+      </c>
+      <c r="H11" s="7">
+        <v>3319.0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>7.599999999999999</v>
+      </c>
+      <c r="J11" s="7">
+        <v>1165.6666666666667</v>
+      </c>
+      <c r="K11" s="7">
+        <v>217.66666666666666</v>
+      </c>
+      <c r="L11" s="3">
+        <v>2.813333333333333</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.8476448729537008</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lastfm_paper_h01</t>
+        </is>
+      </c>
+      <c r="B12" s="7">
+        <v>1892</v>
+      </c>
+      <c r="C12" s="7">
+        <v>25434</v>
+      </c>
+      <c r="D12" s="7">
+        <v>100</v>
+      </c>
+      <c r="E12" s="7">
+        <v>20</v>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O(nC)  Eq (19)  +  sum_c O(n_c * t_c log t_c)  init  +  O(CK) DP cells</t>
+        </is>
+      </c>
+      <c r="L12" s="3">
+        <v>0.4266666666666667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lastfm_paper_h01</t>
+        </is>
+      </c>
+      <c r="B13" s="7">
+        <v>1892</v>
+      </c>
+      <c r="C13" s="7">
+        <v>25434</v>
+      </c>
+      <c r="D13" s="7">
+        <v>100</v>
+      </c>
+      <c r="E13" s="7">
+        <v>20</v>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O(n * t log t)  global init  +  sum_c O(n_c * t log t)  curves  +  O(C K^2) DP  +  O(K * t^2) realisation</t>
+        </is>
+      </c>
+      <c r="H13" s="7">
+        <v>2798.3333333333335</v>
+      </c>
+      <c r="I13" s="6">
+        <v>2.966666666666667</v>
+      </c>
+      <c r="J13" s="7">
+        <v>983.6666666666666</v>
+      </c>
+      <c r="K13" s="7">
+        <v>140.0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.3933333333333333</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.14055985705777246</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delicious_paper_h01</t>
+        </is>
+      </c>
+      <c r="B14" s="7">
+        <v>1861</v>
+      </c>
+      <c r="C14" s="7">
+        <v>15328</v>
+      </c>
+      <c r="D14" s="7">
+        <v>100</v>
+      </c>
+      <c r="E14" s="7">
+        <v>20</v>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O(nC)  Eq (19)  +  sum_c O(n_c * t_c log t_c)  init  +  O(CK) DP cells</t>
+        </is>
+      </c>
+      <c r="L14" s="3">
+        <v>0.05333333333333334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delicious_paper_h01</t>
+        </is>
+      </c>
+      <c r="B15" s="7">
+        <v>1861</v>
+      </c>
+      <c r="C15" s="7">
+        <v>15328</v>
+      </c>
+      <c r="D15" s="7">
+        <v>100</v>
+      </c>
+      <c r="E15" s="7">
+        <v>20</v>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTIM-G</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O(n * t log t)  global init  +  sum_c O(n_c * t log t)  curves  +  O(C K^2) DP  +  O(K * t^2) realisation</t>
+        </is>
+      </c>
+      <c r="H15" s="7">
+        <v>2507.0</v>
+      </c>
+      <c r="I15" s="6">
+        <v>1.1</v>
+      </c>
+      <c r="J15" s="7">
+        <v>752.0</v>
+      </c>
+      <c r="K15" s="7">
+        <v>46.0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0.03191065017949741</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">CTIM has no measured row: ctim_select_seeds builds its MIA objects internally, so the driver cannot read the memo dicts back as counters. Every CTIM/CTIM-G ratio here is wall clock with no primitive count behind it.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Arborescence count is NOT a reliable cost proxy. Measured separately, CTIM-G builds ~17% more arborescences than GlobalGreedy, of larger mean size, yet runs 4.8x faster. The [C] section of run_ctim_global.py claims "(count, mean size) IS the empirical cost"; that claim is refuted.</t>
         </is>
@@ -1527,7 +4215,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
